--- a/distribucion/excel_analisis_datos/codigos/c04_funciones/datos_analisis.xlsx
+++ b/distribucion/excel_analisis_datos/codigos/c04_funciones/datos_analisis.xlsx
@@ -494,23 +494,23 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>373.36</v>
+        <v>200.43</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>373.36</v>
+        <v>4008.66</v>
       </c>
     </row>
     <row r="3">
@@ -521,23 +521,23 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>52.6</v>
+        <v>424.3</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>946.8</v>
+        <v>5091.64</v>
       </c>
     </row>
     <row r="4">
@@ -548,23 +548,23 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>102</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>124</v>
+        <v>163.46</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>868.03</v>
+        <v>817.3099999999999</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>215.56</v>
+        <v>349.78</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>3880.16</v>
+        <v>4197.41</v>
       </c>
     </row>
     <row r="6">
@@ -602,23 +602,23 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>352.09</v>
+        <v>198.02</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2112.53</v>
+        <v>3762.34</v>
       </c>
     </row>
     <row r="7">
@@ -629,23 +629,23 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>60.08</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>660.91</v>
+        <v>1651.75</v>
       </c>
     </row>
     <row r="8">
@@ -656,7 +656,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -666,13 +666,13 @@
         <v>204</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>139.62</v>
+        <v>313.51</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2792.3</v>
+        <v>4702.66</v>
       </c>
     </row>
     <row r="9">
@@ -683,23 +683,23 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>48.61</v>
+        <v>409.46</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>631.96</v>
+        <v>2866.19</v>
       </c>
     </row>
     <row r="10">
@@ -710,23 +710,23 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>202</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>104.22</v>
+        <v>213.66</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1980.21</v>
+        <v>3418.54</v>
       </c>
     </row>
     <row r="11">
@@ -737,23 +737,23 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>429.11</v>
+        <v>25.12</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1287.32</v>
+        <v>477.31</v>
       </c>
     </row>
     <row r="12">
@@ -764,23 +764,23 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>89.7</v>
+        <v>273.43</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1076.41</v>
+        <v>2187.43</v>
       </c>
     </row>
     <row r="13">
@@ -791,23 +791,23 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>321.14</v>
+        <v>260.29</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>6422.79</v>
+        <v>4685.31</v>
       </c>
     </row>
     <row r="14">
@@ -818,23 +818,23 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>195.93</v>
+        <v>413.08</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>2939</v>
+        <v>7435.43</v>
       </c>
     </row>
     <row r="15">
@@ -845,23 +845,23 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>104</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>423</v>
+        <v>60.18</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>4652.97</v>
+        <v>842.58</v>
       </c>
     </row>
     <row r="16">
@@ -872,23 +872,23 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>141.19</v>
+        <v>230.37</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1835.51</v>
+        <v>460.74</v>
       </c>
     </row>
     <row r="17">
@@ -899,23 +899,23 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>203.86</v>
+        <v>390.06</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3261.75</v>
+        <v>1560.24</v>
       </c>
     </row>
     <row r="18">
@@ -926,23 +926,23 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>130.85</v>
+        <v>320.06</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>654.24</v>
+        <v>6401.15</v>
       </c>
     </row>
     <row r="19">
@@ -953,23 +953,23 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>205</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>205.71</v>
+        <v>404.67</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3908.42</v>
+        <v>2832.66</v>
       </c>
     </row>
     <row r="20">
@@ -980,23 +980,23 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>380.33</v>
+        <v>274</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1141</v>
+        <v>5479.93</v>
       </c>
     </row>
     <row r="21">
@@ -1007,23 +1007,23 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>41.13</v>
+        <v>141</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>822.5700000000001</v>
+        <v>2678.96</v>
       </c>
     </row>
     <row r="22">
@@ -1034,23 +1034,23 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>431.78</v>
+        <v>460.2</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>7772.08</v>
+        <v>6442.75</v>
       </c>
     </row>
     <row r="23">
@@ -1061,23 +1061,23 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>64.66</v>
+        <v>81.66</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>711.27</v>
+        <v>653.27</v>
       </c>
     </row>
     <row r="24">
@@ -1088,23 +1088,23 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>486.23</v>
+        <v>79.66</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4376.03</v>
+        <v>1274.63</v>
       </c>
     </row>
     <row r="25">
@@ -1115,23 +1115,23 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>308.4</v>
+        <v>47</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>5242.72</v>
+        <v>705.04</v>
       </c>
     </row>
     <row r="26">
@@ -1142,23 +1142,23 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>168.84</v>
+        <v>232.8</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>3376.73</v>
+        <v>2793.61</v>
       </c>
     </row>
     <row r="27">
@@ -1169,23 +1169,23 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>38.38</v>
+        <v>368.16</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>307.07</v>
+        <v>1104.47</v>
       </c>
     </row>
     <row r="28">
@@ -1196,23 +1196,23 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>202</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>489.21</v>
+        <v>204.88</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1467.64</v>
+        <v>3687.85</v>
       </c>
     </row>
     <row r="29">
@@ -1223,23 +1223,23 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>205</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>473.96</v>
+        <v>168.2</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7583.29</v>
+        <v>1513.84</v>
       </c>
     </row>
     <row r="30">
@@ -1250,23 +1250,23 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>465.17</v>
+        <v>427.69</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3256.17</v>
+        <v>8126.05</v>
       </c>
     </row>
     <row r="31">
@@ -1277,23 +1277,23 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>497.62</v>
+        <v>316.83</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>6469.1</v>
+        <v>1267.31</v>
       </c>
     </row>
     <row r="32">
@@ -1304,23 +1304,23 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>131.47</v>
+        <v>233.69</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>525.9</v>
+        <v>3505.41</v>
       </c>
     </row>
     <row r="33">
@@ -1331,23 +1331,23 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>117.91</v>
+        <v>438.47</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2240.22</v>
+        <v>2630.8</v>
       </c>
     </row>
     <row r="34">
@@ -1358,23 +1358,23 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>453.66</v>
+        <v>192.2</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1360.97</v>
+        <v>576.61</v>
       </c>
     </row>
     <row r="35">
@@ -1385,23 +1385,23 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>337.8</v>
+        <v>365.73</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3040.19</v>
+        <v>3657.34</v>
       </c>
     </row>
     <row r="36">
@@ -1412,23 +1412,23 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>394.46</v>
+        <v>114.58</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3155.71</v>
+        <v>114.58</v>
       </c>
     </row>
     <row r="37">
@@ -1439,23 +1439,23 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>183.61</v>
+        <v>343.19</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2570.48</v>
+        <v>5834.26</v>
       </c>
     </row>
     <row r="38">
@@ -1466,23 +1466,23 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>102</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>207.28</v>
+        <v>350.08</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>414.57</v>
+        <v>4901.05</v>
       </c>
     </row>
     <row r="39">
@@ -1493,23 +1493,23 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>103.2</v>
+        <v>368.07</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>722.42</v>
+        <v>1104.22</v>
       </c>
     </row>
     <row r="40">
@@ -1520,23 +1520,23 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>236.69</v>
+        <v>77.19</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>2130.19</v>
+        <v>771.9299999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>102</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>329.55</v>
+        <v>286.01</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>659.1</v>
+        <v>4862.22</v>
       </c>
     </row>
     <row r="42">
@@ -1574,23 +1574,23 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>202</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>91.48999999999999</v>
+        <v>363.99</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>731.9400000000001</v>
+        <v>4367.9</v>
       </c>
     </row>
     <row r="43">
@@ -1601,23 +1601,23 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>107</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>90.67</v>
+        <v>346.42</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>181.34</v>
+        <v>6928.35</v>
       </c>
     </row>
     <row r="44">
@@ -1628,23 +1628,23 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>217.27</v>
+        <v>298.89</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>2172.74</v>
+        <v>1195.56</v>
       </c>
     </row>
     <row r="45">
@@ -1655,23 +1655,23 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>103.05</v>
+        <v>131.42</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>515.25</v>
+        <v>657.08</v>
       </c>
     </row>
     <row r="46">
@@ -1682,23 +1682,23 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>38.01</v>
+        <v>425.47</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>418.12</v>
+        <v>425.47</v>
       </c>
     </row>
     <row r="47">
@@ -1709,23 +1709,23 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>202</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>480.78</v>
+        <v>154.82</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>961.5599999999999</v>
+        <v>2012.6</v>
       </c>
     </row>
     <row r="48">
@@ -1736,23 +1736,23 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>43.3</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>866.02</v>
+        <v>848.1799999999999</v>
       </c>
     </row>
     <row r="49">
@@ -1763,23 +1763,23 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>301.31</v>
+        <v>445.48</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>5724.97</v>
+        <v>7573.08</v>
       </c>
     </row>
     <row r="50">
@@ -1790,23 +1790,23 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>110.09</v>
+        <v>431.8</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>990.78</v>
+        <v>5613.39</v>
       </c>
     </row>
     <row r="51">
@@ -1817,23 +1817,23 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>74.13</v>
+        <v>477.68</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>963.6900000000001</v>
+        <v>7642.91</v>
       </c>
     </row>
     <row r="52">
@@ -1844,23 +1844,23 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>14.56</v>
+        <v>138.47</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>43.69</v>
+        <v>138.47</v>
       </c>
     </row>
     <row r="53">
@@ -1871,23 +1871,23 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>114.45</v>
+        <v>385.88</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>2060.02</v>
+        <v>6560.03</v>
       </c>
     </row>
     <row r="54">
@@ -1898,23 +1898,23 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>102</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>191.07</v>
+        <v>273.45</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1528.55</v>
+        <v>4922.12</v>
       </c>
     </row>
     <row r="55">
@@ -1925,23 +1925,23 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v>105</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>492.09</v>
+        <v>260.54</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>9841.76</v>
+        <v>781.62</v>
       </c>
     </row>
     <row r="56">
@@ -1952,23 +1952,23 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>201</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>470.08</v>
+        <v>297.35</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1880.3</v>
+        <v>3865.6</v>
       </c>
     </row>
     <row r="57">
@@ -1979,23 +1979,23 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>202</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>86.17</v>
+        <v>367.68</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>1551.05</v>
+        <v>5147.51</v>
       </c>
     </row>
     <row r="58">
@@ -2006,23 +2006,23 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>346.87</v>
+        <v>66.83</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>2428.12</v>
+        <v>935.67</v>
       </c>
     </row>
     <row r="59">
@@ -2033,23 +2033,23 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>105</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>55.23</v>
+        <v>68.53</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>110.45</v>
+        <v>411.16</v>
       </c>
     </row>
     <row r="60">
@@ -2060,23 +2060,23 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>203</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>173.44</v>
+        <v>476.98</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>173.44</v>
+        <v>7631.65</v>
       </c>
     </row>
     <row r="61">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -2097,13 +2097,13 @@
         <v>201</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>280.32</v>
+        <v>72.2</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>4204.85</v>
+        <v>866.35</v>
       </c>
     </row>
     <row r="62">
@@ -2114,23 +2114,23 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>473.07</v>
+        <v>405.48</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1419.22</v>
+        <v>4460.31</v>
       </c>
     </row>
     <row r="63">
@@ -2141,23 +2141,23 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>295.43</v>
+        <v>317.49</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>3545.16</v>
+        <v>6032.33</v>
       </c>
     </row>
     <row r="64">
@@ -2168,23 +2168,23 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>188.68</v>
+        <v>254.81</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>1886.79</v>
+        <v>509.62</v>
       </c>
     </row>
     <row r="65">
@@ -2195,23 +2195,23 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>183.3</v>
+        <v>388.93</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>733.21</v>
+        <v>3500.38</v>
       </c>
     </row>
     <row r="66">
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>201</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>433.66</v>
+        <v>11.26</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>3469.25</v>
+        <v>191.4</v>
       </c>
     </row>
     <row r="67">
@@ -2249,23 +2249,23 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>393.37</v>
+        <v>197.66</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>4327.06</v>
+        <v>2371.92</v>
       </c>
     </row>
     <row r="68">
@@ -2276,23 +2276,23 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>395.81</v>
+        <v>167.68</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>2374.88</v>
+        <v>1341.46</v>
       </c>
     </row>
     <row r="69">
@@ -2303,23 +2303,23 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>107.79</v>
+        <v>290.05</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>862.33</v>
+        <v>870.16</v>
       </c>
     </row>
     <row r="70">
@@ -2330,23 +2330,23 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>21.6</v>
+        <v>404.13</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>172.76</v>
+        <v>3233.01</v>
       </c>
     </row>
     <row r="71">
@@ -2357,23 +2357,23 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>483.78</v>
+        <v>389.03</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>1451.33</v>
+        <v>3890.28</v>
       </c>
     </row>
     <row r="72">
@@ -2384,23 +2384,23 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>203</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>172.26</v>
+        <v>190.77</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>3100.74</v>
+        <v>190.77</v>
       </c>
     </row>
     <row r="73">
@@ -2411,23 +2411,23 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>481.64</v>
+        <v>190.45</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>9151.190000000001</v>
+        <v>2856.81</v>
       </c>
     </row>
     <row r="74">
@@ -2438,23 +2438,23 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>366.99</v>
+        <v>13.13</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>4403.84</v>
+        <v>65.63</v>
       </c>
     </row>
     <row r="75">
@@ -2465,23 +2465,23 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>450.76</v>
+        <v>475.99</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>5859.85</v>
+        <v>475.99</v>
       </c>
     </row>
     <row r="76">
@@ -2492,23 +2492,23 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>264.76</v>
+        <v>110.55</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>264.76</v>
+        <v>442.18</v>
       </c>
     </row>
     <row r="77">
@@ -2519,23 +2519,23 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>44.29</v>
+        <v>358.71</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>620.02</v>
+        <v>1793.55</v>
       </c>
     </row>
     <row r="78">
@@ -2546,23 +2546,23 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>362.68</v>
+        <v>234.64</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>1450.72</v>
+        <v>2815.73</v>
       </c>
     </row>
     <row r="79">
@@ -2573,23 +2573,23 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>207.18</v>
+        <v>75.42</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2278.94</v>
+        <v>1282.17</v>
       </c>
     </row>
     <row r="80">
@@ -2600,23 +2600,23 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>14</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>335.82</v>
+        <v>334.6</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>4701.42</v>
+        <v>4684.37</v>
       </c>
     </row>
     <row r="81">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -2637,13 +2637,13 @@
         <v>203</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>278.49</v>
+        <v>463.76</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>3620.36</v>
+        <v>5101.37</v>
       </c>
     </row>
     <row r="82">
@@ -2654,23 +2654,23 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>395.02</v>
+        <v>143.26</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>5530.31</v>
+        <v>2148.88</v>
       </c>
     </row>
     <row r="83">
@@ -2681,23 +2681,23 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>226.66</v>
+        <v>61.77</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>3399.87</v>
+        <v>308.86</v>
       </c>
     </row>
     <row r="84">
@@ -2708,23 +2708,23 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>149.06</v>
+        <v>272.6</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>447.17</v>
+        <v>1090.41</v>
       </c>
     </row>
     <row r="85">
@@ -2735,23 +2735,23 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>203</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>411.03</v>
+        <v>427.72</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>1233.08</v>
+        <v>3849.45</v>
       </c>
     </row>
     <row r="86">
@@ -2762,23 +2762,23 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>82.2</v>
+        <v>419.6</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>575.42</v>
+        <v>2937.22</v>
       </c>
     </row>
     <row r="87">
@@ -2789,23 +2789,23 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>213.08</v>
+        <v>204.16</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>3196.14</v>
+        <v>2449.92</v>
       </c>
     </row>
     <row r="88">
@@ -2816,23 +2816,23 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>205.83</v>
+        <v>25.23</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>3293.28</v>
+        <v>151.38</v>
       </c>
     </row>
     <row r="89">
@@ -2843,23 +2843,23 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>117.23</v>
+        <v>236.4</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1641.25</v>
+        <v>945.6</v>
       </c>
     </row>
     <row r="90">
@@ -2870,23 +2870,23 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>101</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>132.11</v>
+        <v>74.05</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>2377.93</v>
+        <v>592.4</v>
       </c>
     </row>
     <row r="91">
@@ -2897,23 +2897,23 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>204</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>494.07</v>
+        <v>20.68</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>8399.139999999999</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="92">
@@ -2924,23 +2924,23 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>228.5</v>
+        <v>453.49</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>4112.96</v>
+        <v>1360.46</v>
       </c>
     </row>
     <row r="93">
@@ -2951,23 +2951,23 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v>108</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>378.37</v>
+        <v>92.31</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>3405.34</v>
+        <v>184.63</v>
       </c>
     </row>
     <row r="94">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -2988,13 +2988,13 @@
         <v>203</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>144.55</v>
+        <v>197.54</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>1156.42</v>
+        <v>197.54</v>
       </c>
     </row>
     <row r="95">
@@ -3005,23 +3005,23 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v>104</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>174.57</v>
+        <v>144.74</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>1571.09</v>
+        <v>868.45</v>
       </c>
     </row>
     <row r="96">
@@ -3032,23 +3032,23 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>197.69</v>
+        <v>254.46</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>1581.5</v>
+        <v>2544.57</v>
       </c>
     </row>
     <row r="97">
@@ -3059,23 +3059,23 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>102</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>209.72</v>
+        <v>197.68</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>2936.13</v>
+        <v>1779.1</v>
       </c>
     </row>
     <row r="98">
@@ -3086,23 +3086,23 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>418.12</v>
+        <v>399.47</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>2926.82</v>
+        <v>7190.54</v>
       </c>
     </row>
     <row r="99">
@@ -3113,23 +3113,23 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>196.39</v>
+        <v>392.9</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>3731.35</v>
+        <v>7072.26</v>
       </c>
     </row>
     <row r="100">
@@ -3140,23 +3140,23 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>205</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>273.73</v>
+        <v>142.51</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>3832.19</v>
+        <v>1852.68</v>
       </c>
     </row>
     <row r="101">
@@ -3167,23 +3167,23 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>104</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>117.52</v>
+        <v>448.92</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>1880.27</v>
+        <v>448.92</v>
       </c>
     </row>
     <row r="102">
@@ -3194,23 +3194,23 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>202</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>337.75</v>
+        <v>499.81</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>3715.23</v>
+        <v>9496.33</v>
       </c>
     </row>
     <row r="103">
@@ -3221,23 +3221,23 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>490.55</v>
+        <v>271.51</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>2452.77</v>
+        <v>2443.57</v>
       </c>
     </row>
     <row r="104">
@@ -3248,23 +3248,23 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>324.95</v>
+        <v>468.25</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>974.84</v>
+        <v>5619.01</v>
       </c>
     </row>
     <row r="105">
@@ -3275,23 +3275,23 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>137.48</v>
+        <v>457.85</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>274.95</v>
+        <v>5494.2</v>
       </c>
     </row>
     <row r="106">
@@ -3302,23 +3302,23 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>383</v>
+        <v>474.7</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>4213.03</v>
+        <v>9019.309999999999</v>
       </c>
     </row>
     <row r="107">
@@ -3329,23 +3329,23 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>240.45</v>
+        <v>28.6</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>721.35</v>
+        <v>457.64</v>
       </c>
     </row>
     <row r="108">
@@ -3356,23 +3356,23 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>328.57</v>
+        <v>267.96</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>2628.56</v>
+        <v>267.96</v>
       </c>
     </row>
     <row r="109">
@@ -3383,23 +3383,23 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v>104</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>421.22</v>
+        <v>176.97</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>2948.55</v>
+        <v>884.86</v>
       </c>
     </row>
     <row r="110">
@@ -3410,23 +3410,23 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>338.03</v>
+        <v>82.38</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>5408.56</v>
+        <v>82.38</v>
       </c>
     </row>
     <row r="111">
@@ -3437,23 +3437,23 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>92.22</v>
+        <v>193.06</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>1106.6</v>
+        <v>579.1799999999999</v>
       </c>
     </row>
     <row r="112">
@@ -3464,23 +3464,23 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>62.97</v>
+        <v>157.86</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>629.6799999999999</v>
+        <v>1736.51</v>
       </c>
     </row>
     <row r="113">
@@ -3491,23 +3491,23 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>205</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>471.32</v>
+        <v>95.36</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>6127.17</v>
+        <v>1048.95</v>
       </c>
     </row>
     <row r="114">
@@ -3518,23 +3518,23 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>351.62</v>
+        <v>336.11</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>1406.5</v>
+        <v>2688.88</v>
       </c>
     </row>
     <row r="115">
@@ -3545,23 +3545,23 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>393.49</v>
+        <v>97.08</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>7476.34</v>
+        <v>485.39</v>
       </c>
     </row>
     <row r="116">
@@ -3572,23 +3572,23 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>257.92</v>
+        <v>25.87</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>773.76</v>
+        <v>491.48</v>
       </c>
     </row>
     <row r="117">
@@ -3599,23 +3599,23 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>222.43</v>
+        <v>61.01</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>889.71</v>
+        <v>1159.27</v>
       </c>
     </row>
     <row r="118">
@@ -3626,23 +3626,23 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>96.31</v>
+        <v>179.94</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1348.3</v>
+        <v>1439.5</v>
       </c>
     </row>
     <row r="119">
@@ -3653,23 +3653,23 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>15</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>223.43</v>
+        <v>15.58</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>3351.47</v>
+        <v>233.76</v>
       </c>
     </row>
     <row r="120">
@@ -3680,23 +3680,23 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v>106</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>417.06</v>
+        <v>395.64</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>3336.47</v>
+        <v>3560.76</v>
       </c>
     </row>
     <row r="121">
@@ -3707,23 +3707,23 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>15</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>289.23</v>
+        <v>368.97</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>4338.39</v>
+        <v>5534.5</v>
       </c>
     </row>
     <row r="122">
@@ -3734,23 +3734,23 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>426.97</v>
+        <v>277.55</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>6831.47</v>
+        <v>3330.62</v>
       </c>
     </row>
     <row r="123">
@@ -3761,23 +3761,23 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>176.77</v>
+        <v>231.13</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>1590.89</v>
+        <v>1386.79</v>
       </c>
     </row>
     <row r="124">
@@ -3788,23 +3788,23 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>474.55</v>
+        <v>476.31</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>8067.36</v>
+        <v>4286.83</v>
       </c>
     </row>
     <row r="125">
@@ -3815,23 +3815,23 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>381.5</v>
+        <v>368.67</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>6867.01</v>
+        <v>2212.04</v>
       </c>
     </row>
     <row r="126">
@@ -3842,23 +3842,23 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>108</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>55.6</v>
+        <v>221.35</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>55.6</v>
+        <v>221.35</v>
       </c>
     </row>
     <row r="127">
@@ -3869,23 +3869,23 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>190.82</v>
+        <v>36.24</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>3625.58</v>
+        <v>217.45</v>
       </c>
     </row>
     <row r="128">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
@@ -3909,10 +3909,10 @@
         <v>18</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>172.09</v>
+        <v>363.8</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>3097.58</v>
+        <v>6548.38</v>
       </c>
     </row>
     <row r="129">
@@ -3923,23 +3923,23 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v>105</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>122.96</v>
+        <v>126.4</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>1106.67</v>
+        <v>1263.99</v>
       </c>
     </row>
     <row r="130">
@@ -3950,23 +3950,23 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>475.93</v>
+        <v>36.71</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>8566.74</v>
+        <v>183.54</v>
       </c>
     </row>
     <row r="131">
@@ -3977,23 +3977,23 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>145.48</v>
+        <v>245.36</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>2327.76</v>
+        <v>4907.22</v>
       </c>
     </row>
     <row r="132">
@@ -4004,23 +4004,23 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>417.99</v>
+        <v>488.76</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>1671.95</v>
+        <v>4887.58</v>
       </c>
     </row>
     <row r="133">
@@ -4031,23 +4031,23 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>16.93</v>
+        <v>240.76</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>169.33</v>
+        <v>3129.92</v>
       </c>
     </row>
     <row r="134">
@@ -4058,23 +4058,23 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>281.15</v>
+        <v>191.8</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>562.29</v>
+        <v>1150.8</v>
       </c>
     </row>
     <row r="135">
@@ -4085,23 +4085,23 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>291.29</v>
+        <v>139.02</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>291.29</v>
+        <v>278.03</v>
       </c>
     </row>
     <row r="136">
@@ -4112,23 +4112,23 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>483.09</v>
+        <v>40.2</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>2898.56</v>
+        <v>763.86</v>
       </c>
     </row>
     <row r="137">
@@ -4139,23 +4139,23 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>102</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>206.35</v>
+        <v>406.01</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>619.04</v>
+        <v>4872.1</v>
       </c>
     </row>
     <row r="138">
@@ -4166,23 +4166,23 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>407.46</v>
+        <v>39.88</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>2037.3</v>
+        <v>717.88</v>
       </c>
     </row>
     <row r="139">
@@ -4193,23 +4193,23 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E139" s="2" t="n">
         <v>18</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>384.58</v>
+        <v>346.66</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>6922.39</v>
+        <v>6239.94</v>
       </c>
     </row>
     <row r="140">
@@ -4220,23 +4220,23 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>205</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>196.39</v>
+        <v>48.69</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>3338.55</v>
+        <v>486.88</v>
       </c>
     </row>
     <row r="141">
@@ -4247,23 +4247,23 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>288.63</v>
+        <v>475.13</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>2886.28</v>
+        <v>1900.54</v>
       </c>
     </row>
     <row r="142">
@@ -4274,23 +4274,23 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v>104</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>139.68</v>
+        <v>71.83</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>977.74</v>
+        <v>502.82</v>
       </c>
     </row>
     <row r="143">
@@ -4301,23 +4301,23 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>46.78</v>
+        <v>418.71</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>842.0700000000001</v>
+        <v>2093.56</v>
       </c>
     </row>
     <row r="144">
@@ -4328,23 +4328,23 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>203</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>25.99</v>
+        <v>282.62</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>259.94</v>
+        <v>3674.04</v>
       </c>
     </row>
     <row r="145">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
@@ -4365,13 +4365,13 @@
         <v>205</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>346.82</v>
+        <v>395.41</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>1040.46</v>
+        <v>395.41</v>
       </c>
     </row>
     <row r="146">
@@ -4382,23 +4382,23 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>66.23999999999999</v>
+        <v>213.08</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>927.37</v>
+        <v>852.3099999999999</v>
       </c>
     </row>
     <row r="147">
@@ -4409,23 +4409,23 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>203</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>44.99</v>
+        <v>285.72</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>224.95</v>
+        <v>1142.86</v>
       </c>
     </row>
     <row r="148">
@@ -4436,23 +4436,23 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>70.93000000000001</v>
+        <v>139.43</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>1064</v>
+        <v>1951.98</v>
       </c>
     </row>
     <row r="149">
@@ -4463,23 +4463,23 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>205</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>274.59</v>
+        <v>94.38</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>4668.05</v>
+        <v>188.76</v>
       </c>
     </row>
     <row r="150">
@@ -4490,23 +4490,23 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>369.92</v>
+        <v>203.94</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>5178.9</v>
+        <v>407.88</v>
       </c>
     </row>
     <row r="151">
@@ -4517,23 +4517,23 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>481.34</v>
+        <v>461.21</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>3850.69</v>
+        <v>7379.35</v>
       </c>
     </row>
     <row r="152">
@@ -4544,23 +4544,23 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v>105</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>29.71</v>
+        <v>147.37</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>564.5599999999999</v>
+        <v>1473.7</v>
       </c>
     </row>
     <row r="153">
@@ -4571,23 +4571,23 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>98.93000000000001</v>
+        <v>157.24</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>890.37</v>
+        <v>786.1799999999999</v>
       </c>
     </row>
     <row r="154">
@@ -4598,23 +4598,23 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>180.5</v>
+        <v>306.44</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>2888.01</v>
+        <v>4290.16</v>
       </c>
     </row>
     <row r="155">
@@ -4625,23 +4625,23 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>211.71</v>
+        <v>373.06</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>2328.77</v>
+        <v>5222.88</v>
       </c>
     </row>
     <row r="156">
@@ -4652,23 +4652,23 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v>101</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>53.15</v>
+        <v>397.83</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>797.24</v>
+        <v>6763.11</v>
       </c>
     </row>
     <row r="157">
@@ -4679,23 +4679,23 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v>107</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>414.21</v>
+        <v>392.45</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>7041.64</v>
+        <v>1962.27</v>
       </c>
     </row>
     <row r="158">
@@ -4706,23 +4706,23 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>36.56</v>
+        <v>438.84</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>511.84</v>
+        <v>3071.87</v>
       </c>
     </row>
     <row r="159">
@@ -4733,23 +4733,23 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>382.4</v>
+        <v>233.66</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>5735.93</v>
+        <v>467.32</v>
       </c>
     </row>
     <row r="160">
@@ -4760,23 +4760,23 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>201</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>224.68</v>
+        <v>413.52</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>2246.77</v>
+        <v>4962.22</v>
       </c>
     </row>
     <row r="161">
@@ -4787,23 +4787,23 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v>101</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>401.66</v>
+        <v>192.51</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>8033.27</v>
+        <v>1540.07</v>
       </c>
     </row>
     <row r="162">
@@ -4814,23 +4814,23 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>209.92</v>
+        <v>280.15</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>3778.48</v>
+        <v>5322.92</v>
       </c>
     </row>
     <row r="163">
@@ -4841,23 +4841,23 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>327.38</v>
+        <v>23.45</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>1309.51</v>
+        <v>234.51</v>
       </c>
     </row>
     <row r="164">
@@ -4868,23 +4868,23 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>419.01</v>
+        <v>327.22</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>5866.21</v>
+        <v>2617.73</v>
       </c>
     </row>
     <row r="165">
@@ -4895,23 +4895,23 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>103.4</v>
+        <v>19.83</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>1344.19</v>
+        <v>337.04</v>
       </c>
     </row>
     <row r="166">
@@ -4922,23 +4922,23 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>388.61</v>
+        <v>304.56</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>3497.5</v>
+        <v>1827.36</v>
       </c>
     </row>
     <row r="167">
@@ -4949,23 +4949,23 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v>105</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>148.59</v>
+        <v>217.67</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>148.59</v>
+        <v>1958.99</v>
       </c>
     </row>
     <row r="168">
@@ -4976,23 +4976,23 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v>108</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>228.81</v>
+        <v>116.92</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>1144.04</v>
+        <v>1052.3</v>
       </c>
     </row>
     <row r="169">
@@ -5003,23 +5003,23 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v>107</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>467.1</v>
+        <v>60.13</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>7006.46</v>
+        <v>1142.53</v>
       </c>
     </row>
     <row r="170">
@@ -5030,23 +5030,23 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>203</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>429.45</v>
+        <v>345.36</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>3435.57</v>
+        <v>3453.62</v>
       </c>
     </row>
     <row r="171">
@@ -5057,23 +5057,23 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>199.18</v>
+        <v>432.13</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>2589.32</v>
+        <v>4753.44</v>
       </c>
     </row>
     <row r="172">
@@ -5084,23 +5084,23 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>71.86</v>
+        <v>263.47</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>143.72</v>
+        <v>1317.37</v>
       </c>
     </row>
     <row r="173">
@@ -5111,23 +5111,23 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>267.72</v>
+        <v>343.57</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>1070.86</v>
+        <v>3779.27</v>
       </c>
     </row>
     <row r="174">
@@ -5138,23 +5138,23 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>46.67</v>
+        <v>454.39</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>233.33</v>
+        <v>4089.48</v>
       </c>
     </row>
     <row r="175">
@@ -5165,23 +5165,23 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>205</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>427.36</v>
+        <v>366.01</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>1282.09</v>
+        <v>4026.1</v>
       </c>
     </row>
     <row r="176">
@@ -5192,23 +5192,23 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>205</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>317.13</v>
+        <v>258.58</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>3488.45</v>
+        <v>3103.01</v>
       </c>
     </row>
     <row r="177">
@@ -5219,23 +5219,23 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D177" s="2" t="n">
         <v>203</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>43.53</v>
+        <v>57.83</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>870.52</v>
+        <v>578.26</v>
       </c>
     </row>
     <row r="178">
@@ -5246,23 +5246,23 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>222.65</v>
+        <v>330.67</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>667.9400000000001</v>
+        <v>3637.4</v>
       </c>
     </row>
     <row r="179">
@@ -5273,23 +5273,23 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>203</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>350.06</v>
+        <v>396.16</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>2100.36</v>
+        <v>5546.3</v>
       </c>
     </row>
     <row r="180">
@@ -5300,23 +5300,23 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>185.65</v>
+        <v>427.09</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>1856.47</v>
+        <v>6406.42</v>
       </c>
     </row>
     <row r="181">
@@ -5327,23 +5327,23 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>344.08</v>
+        <v>445.82</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>6537.56</v>
+        <v>7133.1</v>
       </c>
     </row>
     <row r="182">
@@ -5354,23 +5354,23 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D182" s="2" t="n">
         <v>202</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>436.71</v>
+        <v>36.49</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>8734.23</v>
+        <v>510.87</v>
       </c>
     </row>
     <row r="183">
@@ -5381,23 +5381,23 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>203</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>80.13</v>
+        <v>493.72</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>1522.43</v>
+        <v>6912.13</v>
       </c>
     </row>
     <row r="184">
@@ -5408,23 +5408,23 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>336.75</v>
+        <v>248.91</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>3030.77</v>
+        <v>746.74</v>
       </c>
     </row>
     <row r="185">
@@ -5435,23 +5435,23 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>226.45</v>
+        <v>231.51</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>679.34</v>
+        <v>231.51</v>
       </c>
     </row>
     <row r="186">
@@ -5462,23 +5462,23 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>233.85</v>
+        <v>394.75</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>2104.65</v>
+        <v>6316.05</v>
       </c>
     </row>
     <row r="187">
@@ -5489,23 +5489,23 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>126.23</v>
+        <v>207.66</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>504.92</v>
+        <v>2907.28</v>
       </c>
     </row>
     <row r="188">
@@ -5516,23 +5516,23 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>203</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>20.75</v>
+        <v>107.71</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>207.5</v>
+        <v>1938.83</v>
       </c>
     </row>
     <row r="189">
@@ -5543,23 +5543,23 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>433.88</v>
+        <v>341.61</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>8243.780000000001</v>
+        <v>341.61</v>
       </c>
     </row>
     <row r="190">
@@ -5570,23 +5570,23 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>390.11</v>
+        <v>162.93</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>3901.13</v>
+        <v>1955.1</v>
       </c>
     </row>
     <row r="191">
@@ -5597,23 +5597,23 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>314.24</v>
+        <v>41.99</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>2199.66</v>
+        <v>251.94</v>
       </c>
     </row>
     <row r="192">
@@ -5624,23 +5624,23 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>161.38</v>
+        <v>302.22</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>322.75</v>
+        <v>5137.76</v>
       </c>
     </row>
     <row r="193">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
@@ -5661,13 +5661,13 @@
         <v>204</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>54.17</v>
+        <v>186.03</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>270.83</v>
+        <v>2976.53</v>
       </c>
     </row>
     <row r="194">
@@ -5678,23 +5678,23 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>74.76000000000001</v>
+        <v>119.92</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>523.3099999999999</v>
+        <v>959.34</v>
       </c>
     </row>
     <row r="195">
@@ -5705,23 +5705,23 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>135.92</v>
+        <v>189.63</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>815.49</v>
+        <v>758.52</v>
       </c>
     </row>
     <row r="196">
@@ -5732,23 +5732,23 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>239.48</v>
+        <v>387.91</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>957.9299999999999</v>
+        <v>3491.21</v>
       </c>
     </row>
     <row r="197">
@@ -5759,23 +5759,23 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>189.23</v>
+        <v>330.25</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>3406.14</v>
+        <v>1320.99</v>
       </c>
     </row>
     <row r="198">
@@ -5786,23 +5786,23 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E198" s="2" t="n">
         <v>15</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>190.61</v>
+        <v>196.32</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>2859.1</v>
+        <v>2944.87</v>
       </c>
     </row>
     <row r="199">
@@ -5813,23 +5813,23 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>63.09</v>
+        <v>350.64</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>757.08</v>
+        <v>2454.51</v>
       </c>
     </row>
     <row r="200">
@@ -5840,23 +5840,23 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>118.47</v>
+        <v>334.62</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>2369.4</v>
+        <v>1338.47</v>
       </c>
     </row>
     <row r="201">
@@ -5867,23 +5867,23 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>14</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>67.17</v>
+        <v>417.02</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>940.4</v>
+        <v>5838.28</v>
       </c>
     </row>
   </sheetData>
